--- a/ZonasEscolares/excels/PIURA-PIURA-CASTILLA.xlsx
+++ b/ZonasEscolares/excels/PIURA-PIURA-CASTILLA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/PIURA-PIURA-CASTILLA.xlsx
+++ b/ZonasEscolares/excels/PIURA-PIURA-CASTILLA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>PITAGORAS</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-5.19107</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-80.60361</v>
-      </c>
-      <c r="I2" t="n">
-        <v>291</v>
-      </c>
-      <c r="J2" t="n">
-        <v>13</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-5.19107</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-80.60361</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>007 ANTELA BALAREZO DE BALAREZO</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-5.19463</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-80.61998</v>
-      </c>
-      <c r="I3" t="n">
-        <v>203</v>
-      </c>
-      <c r="J3" t="n">
-        <v>9</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-5.19463</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-80.61998</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>DIVINO NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-5.2261</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-80.61923</v>
-      </c>
-      <c r="I4" t="n">
-        <v>212</v>
-      </c>
-      <c r="J4" t="n">
-        <v>11</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-5.2261</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-80.61923</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>029 SAN BERNARDO</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-5.22292</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-80.62524999999999</v>
-      </c>
-      <c r="I5" t="n">
-        <v>208</v>
-      </c>
-      <c r="J5" t="n">
-        <v>9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-5.22292</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-80.62525</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>490</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-5.19358</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-80.60787000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>11</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-5.19358</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-80.60787</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>MARISCAL RAMON CASTILLA</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-5.19948</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-80.62168</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1519</v>
-      </c>
-      <c r="J7" t="n">
-        <v>63</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-5.19948</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-80.62168</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>ALFEREZ FAP SAMUEL ORDOÑEZ VELASQUEZ</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-5.195546</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-80.61819300000001</v>
-      </c>
-      <c r="I8" t="n">
-        <v>512</v>
-      </c>
-      <c r="J8" t="n">
-        <v>57</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-5.195546</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-80.618193</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>JOSEMARIA ESCRIVA DE BALAGUER</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-5.21052</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-80.62473</v>
-      </c>
-      <c r="I9" t="n">
-        <v>784</v>
-      </c>
-      <c r="J9" t="n">
-        <v>37</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-5.21052</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-80.62473</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>14112 AUGUSTO TIMANA SOSA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-5.21547</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-80.62791</v>
-      </c>
-      <c r="I10" t="n">
-        <v>270</v>
-      </c>
-      <c r="J10" t="n">
-        <v>14</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-5.21547</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-80.62791</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>14114</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-5.22446</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-80.62824000000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>438</v>
-      </c>
-      <c r="J11" t="n">
-        <v>21</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-5.22446</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-80.62824</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>14116 SAN MARTIN DE PORRAS</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-5.21725</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-80.62649</v>
-      </c>
-      <c r="I12" t="n">
-        <v>444</v>
-      </c>
-      <c r="J12" t="n">
-        <v>21</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-5.21725</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-80.62649</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>14118 MARINA PURIZACA BENITES</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-5.22685</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-80.61917</v>
-      </c>
-      <c r="I13" t="n">
-        <v>682</v>
-      </c>
-      <c r="J13" t="n">
-        <v>27</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-5.22685</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-80.61917</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>15014 MANUEL HIDALGO CARNERO</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-5.20703</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-80.62148000000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1056</v>
-      </c>
-      <c r="J14" t="n">
-        <v>55</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-5.20703</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-80.62148</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1056</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>15015 HEROES DEL CENEPA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-5.19918</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-80.62124</v>
-      </c>
-      <c r="I15" t="n">
-        <v>250</v>
-      </c>
-      <c r="J15" t="n">
-        <v>12</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-5.19918</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-80.62124</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>15181</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-5.07948</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-80.59348</v>
-      </c>
-      <c r="I16" t="n">
-        <v>531</v>
-      </c>
-      <c r="J16" t="n">
-        <v>24</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-5.07948</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-80.59348</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>SANTISIMA VIRGEN DE GUADALUPE</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-4.985086</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-80.57477799999999</v>
-      </c>
-      <c r="I17" t="n">
-        <v>813</v>
-      </c>
-      <c r="J17" t="n">
-        <v>44</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-4.985086</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-80.574778</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>15186</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-5.04579</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-80.608701</v>
-      </c>
-      <c r="I18" t="n">
-        <v>386</v>
-      </c>
-      <c r="J18" t="n">
-        <v>21</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-5.04579</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-80.608701</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>15350 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-5.18941</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-80.60686</v>
-      </c>
-      <c r="I19" t="n">
-        <v>653</v>
-      </c>
-      <c r="J19" t="n">
-        <v>24</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-5.18941</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-80.60686</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>20017 DIVINO JESUS</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-5.18744</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-80.59259</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1133</v>
-      </c>
-      <c r="J20" t="n">
-        <v>43</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-5.18744</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-80.59259</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1133</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>MARIA GORETTI</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-5.190515</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-80.61026099999999</v>
-      </c>
-      <c r="I21" t="n">
-        <v>778</v>
-      </c>
-      <c r="J21" t="n">
-        <v>27</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-5.190515</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-80.610261</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>CAP. FAP JOSE ABELARDO QUIÑONES</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-5.18932</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-80.59484999999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1506</v>
-      </c>
-      <c r="J22" t="n">
-        <v>47</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-5.18932</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-80.59485</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1506</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>20133</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-5.18444</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-80.5913</v>
-      </c>
-      <c r="I23" t="n">
-        <v>830</v>
-      </c>
-      <c r="J23" t="n">
-        <v>30</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-5.18444</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-80.5913</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>20134</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-5.19182</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-80.60115</v>
-      </c>
-      <c r="I24" t="n">
-        <v>700</v>
-      </c>
-      <c r="J24" t="n">
-        <v>30</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-5.19182</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-80.60115</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-5.185655</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-80.59774899999999</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2343</v>
-      </c>
-      <c r="J25" t="n">
-        <v>87</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-5.185655</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-80.597749</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2343</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>TENIENTE MIGUEL CORTES DEL CASTILLO</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-5.21591</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-80.62369</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1769</v>
-      </c>
-      <c r="J26" t="n">
-        <v>89</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-5.21591</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-80.62369</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1769</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>SAN JOSE DE TARBES</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-5.19509</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-80.61893999999999</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1705</v>
-      </c>
-      <c r="J27" t="n">
-        <v>69</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-5.19509</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-80.61894</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>MANUEL SCORZA</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-5.18625</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-80.60890999999999</v>
-      </c>
-      <c r="I28" t="n">
-        <v>638</v>
-      </c>
-      <c r="J28" t="n">
-        <v>34</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-5.18625</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-80.60891</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>MILITAR PEDRO RUIZ GALLO</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-5.18897</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-80.6009</v>
-      </c>
-      <c r="I29" t="n">
-        <v>244</v>
-      </c>
-      <c r="J29" t="n">
-        <v>21</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-5.18897</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-80.6009</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>PROYECTO PESTALOZZI</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-5.19089</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-80.60785</v>
-      </c>
-      <c r="I30" t="n">
-        <v>229</v>
-      </c>
-      <c r="J30" t="n">
-        <v>16</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-5.19089</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-80.60785</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>RICARDO PALMA</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-5.19846</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-80.6202</v>
-      </c>
-      <c r="I31" t="n">
-        <v>417</v>
-      </c>
-      <c r="J31" t="n">
-        <v>21</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-5.19846</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-80.6202</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>SAN GABRIEL</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-5.18503</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-80.62067</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1146</v>
-      </c>
-      <c r="J32" t="n">
-        <v>55</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-5.18503</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-80.62067</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1146</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>SAN IGNACIO DE LOYOLA DE PIURA</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-5.187135</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-80.619294</v>
-      </c>
-      <c r="I33" t="n">
-        <v>887</v>
-      </c>
-      <c r="J33" t="n">
-        <v>65</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-5.187135</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-80.619294</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>SAN JUDAS TADEO</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-5.18614</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-80.59293</v>
-      </c>
-      <c r="I34" t="n">
-        <v>357</v>
-      </c>
-      <c r="J34" t="n">
-        <v>28</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-5.18614</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-80.59293</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>JAVIER PEREZ DE CUELLAR</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-5.18783</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-80.6082</v>
-      </c>
-      <c r="I35" t="n">
-        <v>519</v>
-      </c>
-      <c r="J35" t="n">
-        <v>26</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-5.18783</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-80.6082</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>ALFONSO UGARTE</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-5.19416</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-80.62027</v>
-      </c>
-      <c r="I36" t="n">
-        <v>218</v>
-      </c>
-      <c r="J36" t="n">
-        <v>28</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-5.19416</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-80.62027</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>FE Y ALEGRIA 15</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-5.227286</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-80.61153</v>
-      </c>
-      <c r="I37" t="n">
-        <v>901</v>
-      </c>
-      <c r="J37" t="n">
-        <v>43</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-5.227286</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-80.61153</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>SALESIANO DON BOSCO</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-5.19533</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-80.62204</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1135</v>
-      </c>
-      <c r="J38" t="n">
-        <v>72</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-5.19533</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-80.62204</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1135</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>VIRGEN DE LA PUERTA</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-5.205272</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-80.621655</v>
-      </c>
-      <c r="I39" t="n">
-        <v>139</v>
-      </c>
-      <c r="J39" t="n">
-        <v>11</v>
-      </c>
-      <c r="K39" t="n">
-        <v>1</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-5.205272</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-80.621655</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>ESTRELLA DE GUADALUPE</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-5.20019</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-80.61901</v>
-      </c>
-      <c r="I40" t="n">
-        <v>238</v>
-      </c>
-      <c r="J40" t="n">
-        <v>13</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-5.20019</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-80.61901</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>15419</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-5.14307</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-80.36602000000001</v>
-      </c>
-      <c r="I41" t="n">
-        <v>210</v>
-      </c>
-      <c r="J41" t="n">
-        <v>13</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-5.14307</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-80.36602</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>LOS ANGELITOS DE SAN ANTONIO</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-5.19121</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-80.60354</v>
-      </c>
-      <c r="I42" t="n">
-        <v>759</v>
-      </c>
-      <c r="J42" t="n">
-        <v>35</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-5.19121</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-80.60354</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>EL TRIUNFO</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-5.197957</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-80.62302800000001</v>
-      </c>
-      <c r="I43" t="n">
-        <v>510</v>
-      </c>
-      <c r="J43" t="n">
-        <v>22</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-5.197957</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-80.623028</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>DIVINO NIÑO</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-5.20865</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-80.62557</v>
-      </c>
-      <c r="I44" t="n">
-        <v>319</v>
-      </c>
-      <c r="J44" t="n">
-        <v>36</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-5.20865</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-80.62557</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>1042</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-5.189801</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-80.580096</v>
-      </c>
-      <c r="I45" t="n">
-        <v>323</v>
-      </c>
-      <c r="J45" t="n">
-        <v>13</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-5.189801</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-80.580096</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>PASITOS</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-5.22012</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-80.62325</v>
-      </c>
-      <c r="I46" t="n">
-        <v>202</v>
-      </c>
-      <c r="J46" t="n">
-        <v>7</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-5.22012</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-80.62325</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>CARLOTA RAMOS DE SANTOLAYA</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-5.18341</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-80.61687999999999</v>
-      </c>
-      <c r="I47" t="n">
-        <v>916</v>
-      </c>
-      <c r="J47" t="n">
-        <v>50</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-5.18341</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-80.61688</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>916</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>R.M. RAFAELA DE LA PASION VEINTEMILLA</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-5.18643</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-80.61171</v>
-      </c>
-      <c r="I48" t="n">
-        <v>219</v>
-      </c>
-      <c r="J48" t="n">
-        <v>23</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-5.18643</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-80.61171</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>TRILCE DE PIURA</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-5.18708</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-80.62016</v>
-      </c>
-      <c r="I49" t="n">
-        <v>333</v>
-      </c>
-      <c r="J49" t="n">
-        <v>21</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-5.18708</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-80.62016</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>1365</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-5.19377</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-80.57765000000001</v>
-      </c>
-      <c r="I50" t="n">
-        <v>236</v>
-      </c>
-      <c r="J50" t="n">
-        <v>11</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-5.19377</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-80.57765</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>1409</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-5.190141</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-80.58282</v>
-      </c>
-      <c r="I51" t="n">
-        <v>67</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2</v>
-      </c>
-      <c r="K51" t="n">
-        <v>1</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-5.190141</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-80.58282</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>15035 FELIX JOAQUIN SEMINARIO ECHEANDIA</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-5.19015</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-80.59011</v>
-      </c>
-      <c r="I52" t="n">
-        <v>280</v>
-      </c>
-      <c r="J52" t="n">
-        <v>14</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-5.19015</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-80.59011</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>1543</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-5.19608</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-80.59545</v>
-      </c>
-      <c r="I53" t="n">
-        <v>290</v>
-      </c>
-      <c r="J53" t="n">
-        <v>14</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-5.19608</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-80.59545</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>MIS PEQUEÑOS TALENTOS</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-5.18749</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-80.61302000000001</v>
-      </c>
-      <c r="I54" t="n">
-        <v>25</v>
-      </c>
-      <c r="J54" t="n">
-        <v>1</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-5.18749</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-80.61302</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>INTELLECTUS</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-5.19316</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-80.62066</v>
-      </c>
-      <c r="I55" t="n">
-        <v>214</v>
-      </c>
-      <c r="J55" t="n">
-        <v>8</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-5.19316</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-80.62066</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>PEQUEÑITOS</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-5.191693</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-80.61814800000001</v>
-      </c>
-      <c r="I56" t="n">
-        <v>72</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-5.191693</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-80.618148</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>PREMIUM</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-5.18581</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-80.623</v>
-      </c>
-      <c r="I57" t="n">
-        <v>1172</v>
-      </c>
-      <c r="J57" t="n">
-        <v>42</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-5.18581</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-80.623</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1172</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>EL TRIUNFO</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-5.20792</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-80.62555</v>
-      </c>
-      <c r="I58" t="n">
-        <v>931</v>
-      </c>
-      <c r="J58" t="n">
-        <v>39</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-5.20792</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-80.62555</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>EXITUS</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-5.16866</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-80.61411</v>
-      </c>
-      <c r="I59" t="n">
-        <v>817</v>
-      </c>
-      <c r="J59" t="n">
-        <v>48</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-5.16866</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-80.61411</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/PIURA-PIURA-CASTILLA.xlsx
+++ b/ZonasEscolares/excels/PIURA-PIURA-CASTILLA.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>32082</t>
+          <t>412299</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PITAGORAS</t>
+          <t>490</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-5.19107</t>
+          <t>-5.19358</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-80.60361</t>
+          <t>-80.60787</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>412176</t>
+          <t>829453</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>007 ANTELA BALAREZO DE BALAREZO</t>
+          <t>MIS PEQUEÑOS TALENTOS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-5.19463</t>
+          <t>-5.18749</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-80.61998</t>
+          <t>-80.61302</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>412195</t>
+          <t>841997</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DIVINO NIÑO JESUS</t>
+          <t>PEQUEÑITOS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.2261</t>
+          <t>-5.191693</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-80.61923</t>
+          <t>-80.618148</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>412204</t>
+          <t>412195</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>029 SAN BERNARDO</t>
+          <t>DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.22292</t>
+          <t>-5.2261</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-80.62525</t>
+          <t>-80.61923</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>212</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>412299</t>
+          <t>413067</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>VIRGEN DE LA PUERTA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.19358</t>
+          <t>-5.205272</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-80.60787</t>
+          <t>-80.621655</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>412341</t>
+          <t>796160</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MARISCAL RAMON CASTILLA</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.19948</t>
+          <t>-5.19377</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-80.62168</t>
+          <t>-80.57765</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>236</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>412355</t>
+          <t>412497</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ALFEREZ FAP SAMUEL ORDOÑEZ VELASQUEZ</t>
+          <t>15015 HEROES DEL CENEPA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.195546</t>
+          <t>-5.19918</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-80.618193</t>
+          <t>-80.62124</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>412379</t>
+          <t>32082</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JOSEMARIA ESCRIVA DE BALAGUER</t>
+          <t>PITAGORAS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.21052</t>
+          <t>-5.19107</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-80.62473</t>
+          <t>-80.60361</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>291</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>412384</t>
+          <t>413072</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14112 AUGUSTO TIMANA SOSA</t>
+          <t>ESTRELLA DE GUADALUPE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-5.21547</t>
+          <t>-5.20019</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-80.62791</t>
+          <t>-80.61901</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>412402</t>
+          <t>430081</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>14114</t>
+          <t>15419</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.22446</t>
+          <t>-5.14307</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-80.62824</t>
+          <t>-80.36602</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>210</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>412416</t>
+          <t>660294</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>14116 SAN MARTIN DE PORRAS</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-5.21725</t>
+          <t>-5.189801</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-80.62649</t>
+          <t>-80.580096</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>323</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>412435</t>
+          <t>412384</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>14118 MARINA PURIZACA BENITES</t>
+          <t>14112 AUGUSTO TIMANA SOSA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.22685</t>
+          <t>-5.21547</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-80.61917</t>
+          <t>-80.62791</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>270</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>412483</t>
+          <t>806569</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>15014 MANUEL HIDALGO CARNERO</t>
+          <t>15035 FELIX JOAQUIN SEMINARIO ECHEANDIA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-5.20703</t>
+          <t>-5.19015</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-80.62148</t>
+          <t>-80.59011</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>280</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>412497</t>
+          <t>820527</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>15015 HEROES DEL CENEPA</t>
+          <t>1543</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.19918</t>
+          <t>-5.19608</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-80.62124</t>
+          <t>-80.59545</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>290</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>412534</t>
+          <t>412765</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>15181</t>
+          <t>PROYECTO PESTALOZZI</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-5.07948</t>
+          <t>-5.19089</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-80.59348</t>
+          <t>-80.60785</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>229</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,37 +1431,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>412548</t>
+          <t>796693</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SANTISIMA VIRGEN DE GUADALUPE</t>
+          <t>1409</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-4.985086</t>
+          <t>-5.190141</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-80.574778</t>
+          <t>-80.58282</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>67</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1493,27 +1493,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>412567</t>
+          <t>412402</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>15186</t>
+          <t>14114</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-5.04579</t>
+          <t>-5.22446</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-80.608701</t>
+          <t>-80.62824</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>438</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>412586</t>
+          <t>412416</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>15350 SAN FRANCISCO DE ASIS</t>
+          <t>14116 SAN MARTIN DE PORRAS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-5.18941</t>
+          <t>-5.21725</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-80.60686</t>
+          <t>-80.62649</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>444</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>412591</t>
+          <t>412567</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20017 DIVINO JESUS</t>
+          <t>15186</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-5.18744</t>
+          <t>-5.04579</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-80.59259</t>
+          <t>-80.608701</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>386</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>412609</t>
+          <t>412708</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MARIA GORETTI</t>
+          <t>MILITAR PEDRO RUIZ GALLO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-5.190515</t>
+          <t>-5.18897</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-80.610261</t>
+          <t>-80.6009</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>244</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>412614</t>
+          <t>412812</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CAP. FAP JOSE ABELARDO QUIÑONES</t>
+          <t>RICARDO PALMA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-5.18932</t>
+          <t>-5.19846</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-80.59485</t>
+          <t>-80.6202</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>417</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>412628</t>
+          <t>766912</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>20133</t>
+          <t>TRILCE DE PIURA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-5.18444</t>
+          <t>-5.18708</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-80.5913</t>
+          <t>-80.62016</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>333</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>412633</t>
+          <t>536493</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>EL TRIUNFO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.19182</t>
+          <t>-5.197957</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-80.60115</t>
+          <t>-80.623028</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>510</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>412647</t>
+          <t>766865</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JOSE CARLOS MARIATEGUI</t>
+          <t>R.M. RAFAELA DE LA PASION VEINTEMILLA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-5.185655</t>
+          <t>-5.18643</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-80.597749</t>
+          <t>-80.61171</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>219</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>412652</t>
+          <t>412534</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TENIENTE MIGUEL CORTES DEL CASTILLO</t>
+          <t>15181</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-5.21591</t>
+          <t>-5.07948</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-80.62369</t>
+          <t>-80.59348</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>531</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>412666</t>
+          <t>412586</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SAN JOSE DE TARBES</t>
+          <t>15350 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-5.19509</t>
+          <t>-5.18941</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-80.61894</t>
+          <t>-80.60686</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>653</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>412685</t>
+          <t>412888</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MANUEL SCORZA</t>
+          <t>JAVIER PEREZ DE CUELLAR</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-5.18625</t>
+          <t>-5.18783</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-80.60891</t>
+          <t>-80.6082</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>519</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>412708</t>
+          <t>412435</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MILITAR PEDRO RUIZ GALLO</t>
+          <t>14118 MARINA PURIZACA BENITES</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-5.18897</t>
+          <t>-5.22685</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-80.6009</t>
+          <t>-80.61917</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>682</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>412765</t>
+          <t>412609</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PROYECTO PESTALOZZI</t>
+          <t>MARIA GORETTI</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-5.19089</t>
+          <t>-5.190515</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-80.60785</t>
+          <t>-80.610261</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>778</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>412812</t>
+          <t>412845</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RICARDO PALMA</t>
+          <t>SAN JUDAS TADEO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-5.19846</t>
+          <t>-5.18614</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-80.6202</t>
+          <t>-80.59293</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>357</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>412826</t>
+          <t>412893</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SAN GABRIEL</t>
+          <t>ALFONSO UGARTE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-5.18503</t>
+          <t>-5.19416</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-80.62067</t>
+          <t>-80.62027</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>218</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>412831</t>
+          <t>412628</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE LOYOLA DE PIURA</t>
+          <t>20133</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-5.187135</t>
+          <t>-5.18444</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-80.619294</t>
+          <t>-80.5913</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>830</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>412845</t>
+          <t>412633</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SAN JUDAS TADEO</t>
+          <t>20134</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-5.18614</t>
+          <t>-5.19182</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-80.59293</t>
+          <t>-80.60115</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>700</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>412888</t>
+          <t>412685</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>JAVIER PEREZ DE CUELLAR</t>
+          <t>MANUEL SCORZA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-5.18783</t>
+          <t>-5.18625</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-80.6082</t>
+          <t>-80.60891</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>638</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>412893</t>
+          <t>509102</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ALFONSO UGARTE</t>
+          <t>LOS ANGELITOS DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-5.19416</t>
+          <t>-5.19121</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-80.62027</t>
+          <t>-80.60354</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>759</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>412906</t>
+          <t>609366</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 15</t>
+          <t>DIVINO NIÑO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-5.227286</t>
+          <t>-5.20865</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-80.61153</t>
+          <t>-80.62557</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>319</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>412930</t>
+          <t>412379</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SALESIANO DON BOSCO</t>
+          <t>JOSEMARIA ESCRIVA DE BALAGUER</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-5.19533</t>
+          <t>-5.21052</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-80.62204</t>
+          <t>-80.62473</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>784</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,37 +2795,37 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>413067</t>
+          <t>858327</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>VIRGEN DE LA PUERTA</t>
+          <t>EL TRIUNFO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-5.205272</t>
+          <t>-5.20792</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-80.621655</t>
+          <t>-80.62555</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>931</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>413072</t>
+          <t>852090</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ESTRELLA DE GUADALUPE</t>
+          <t>PREMIUM</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-5.20019</t>
+          <t>-5.18581</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-80.61901</t>
+          <t>-80.623</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>430081</t>
+          <t>412591</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>15419</t>
+          <t>20017 DIVINO JESUS</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-5.14307</t>
+          <t>-5.18744</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-80.36602</t>
+          <t>-80.59259</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>509102</t>
+          <t>412906</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>LOS ANGELITOS DE SAN ANTONIO</t>
+          <t>FE Y ALEGRIA 15</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-5.19121</t>
+          <t>-5.227286</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-80.60354</t>
+          <t>-80.61153</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>901</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>536493</t>
+          <t>412548</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>EL TRIUNFO</t>
+          <t>SANTISIMA VIRGEN DE GUADALUPE</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-5.197957</t>
+          <t>-4.985086</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-80.623028</t>
+          <t>-80.574778</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>813</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>609366</t>
+          <t>412614</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>DIVINO NIÑO</t>
+          <t>CAP. FAP JOSE ABELARDO QUIÑONES</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-5.20865</t>
+          <t>-5.18932</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-80.62557</t>
+          <t>-80.59485</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>660294</t>
+          <t>864781</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>EXITUS</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-5.189801</t>
+          <t>-5.16866</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-80.580096</t>
+          <t>-80.61411</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>817</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>722471</t>
+          <t>766064</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>PASITOS</t>
+          <t>CARLOTA RAMOS DE SANTOLAYA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-5.22012</t>
+          <t>-5.18341</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-80.62325</t>
+          <t>-80.61688</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>916</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>766064</t>
+          <t>412483</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CARLOTA RAMOS DE SANTOLAYA</t>
+          <t>15014 MANUEL HIDALGO CARNERO</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-5.18341</t>
+          <t>-5.20703</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-80.61688</t>
+          <t>-80.62148</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>766865</t>
+          <t>412826</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>R.M. RAFAELA DE LA PASION VEINTEMILLA</t>
+          <t>SAN GABRIEL</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-5.18643</t>
+          <t>-5.18503</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-80.61171</t>
+          <t>-80.62067</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>766912</t>
+          <t>412355</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>TRILCE DE PIURA</t>
+          <t>ALFEREZ FAP SAMUEL ORDOÑEZ VELASQUEZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-5.18708</t>
+          <t>-5.195546</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-80.62016</t>
+          <t>-80.618193</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>512</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>796160</t>
+          <t>412341</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>MARISCAL RAMON CASTILLA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-5.19377</t>
+          <t>-5.19948</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-80.57765</t>
+          <t>-80.62168</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,37 +3539,37 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>796693</t>
+          <t>412831</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>SAN IGNACIO DE LOYOLA DE PIURA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-5.190141</t>
+          <t>-5.187135</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-80.58282</t>
+          <t>-80.619294</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>887</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>806569</t>
+          <t>412666</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>15035 FELIX JOAQUIN SEMINARIO ECHEANDIA</t>
+          <t>SAN JOSE DE TARBES</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-5.19015</t>
+          <t>-5.19509</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-80.59011</t>
+          <t>-80.61894</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>820527</t>
+          <t>722471</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>PASITOS</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-5.19608</t>
+          <t>-5.22012</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-80.59545</t>
+          <t>-80.62325</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>202</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,37 +3725,37 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>829453</t>
+          <t>412930</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MIS PEQUEÑOS TALENTOS</t>
+          <t>SALESIANO DON BOSCO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-5.18749</t>
+          <t>-5.19533</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-80.61302</t>
+          <t>-80.62204</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3849,37 +3849,37 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>841997</t>
+          <t>412647</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PEQUEÑITOS</t>
+          <t>JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-5.191693</t>
+          <t>-5.185655</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-80.618148</t>
+          <t>-80.597749</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>87</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>852090</t>
+          <t>412652</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>TENIENTE MIGUEL CORTES DEL CASTILLO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-5.18581</t>
+          <t>-5.21591</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-80.623</t>
+          <t>-80.62369</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>89</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>858327</t>
+          <t>412176</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>EL TRIUNFO</t>
+          <t>007 ANTELA BALAREZO DE BALAREZO</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-5.20792</t>
+          <t>-5.19463</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-80.62555</t>
+          <t>-80.61998</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>203</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>864781</t>
+          <t>412204</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>EXITUS</t>
+          <t>029 SAN BERNARDO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-5.16866</t>
+          <t>-5.22292</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-80.61411</t>
+          <t>-80.62525</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>208</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">

--- a/ZonasEscolares/excels/PIURA-PIURA-CASTILLA.xlsx
+++ b/ZonasEscolares/excels/PIURA-PIURA-CASTILLA.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>412299</t>
+          <t>864781</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>EXITUS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-5.19358</t>
+          <t>817</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-80.60787</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-5.16866</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-80.61411</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>829453</t>
+          <t>858327</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MIS PEQUEÑOS TALENTOS</t>
+          <t>EL TRIUNFO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-5.18749</t>
+          <t>931</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-80.61302</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-5.20792</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-80.62555</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>841997</t>
+          <t>852090</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PEQUEÑITOS</t>
+          <t>PREMIUM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.191693</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-80.618148</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-5.18581</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-80.623</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>412195</t>
+          <t>841997</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DIVINO NIÑO JESUS</t>
+          <t>PEQUEÑITOS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.2261</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-80.61923</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>-5.191693</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-80.618148</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -749,37 +749,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>413067</t>
+          <t>841978</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VIRGEN DE LA PUERTA</t>
+          <t>INTELLECTUS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.205272</t>
+          <t>214</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-80.621655</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>-5.19316</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-80.62066</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>796160</t>
+          <t>829453</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>MIS PEQUEÑOS TALENTOS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.19377</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-80.57765</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>-5.18749</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-80.61302</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>412497</t>
+          <t>820527</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>15015 HEROES DEL CENEPA</t>
+          <t>1543</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.19918</t>
+          <t>290</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-80.62124</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>-5.19608</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-80.59545</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>32082</t>
+          <t>806569</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PITAGORAS</t>
+          <t>15035 FELIX JOAQUIN SEMINARIO ECHEANDIA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.19107</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-80.60361</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>-5.19015</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-80.59011</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,42 +997,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>413072</t>
+          <t>796693</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ESTRELLA DE GUADALUPE</t>
+          <t>1409</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-5.20019</t>
+          <t>67</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-80.61901</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>-5.190141</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-80.58282</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>430081</t>
+          <t>796160</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>15419</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.14307</t>
+          <t>236</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-80.36602</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>-5.19377</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-80.57765</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>660294</t>
+          <t>766912</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>TRILCE DE PIURA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-5.189801</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-80.580096</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>-5.18708</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-80.62016</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>412384</t>
+          <t>766865</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>14112 AUGUSTO TIMANA SOSA</t>
+          <t>R.M. RAFAELA DE LA PASION VEINTEMILLA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.21547</t>
+          <t>219</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-80.62791</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>-5.18643</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-80.61171</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>806569</t>
+          <t>766064</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>15035 FELIX JOAQUIN SEMINARIO ECHEANDIA</t>
+          <t>CARLOTA RAMOS DE SANTOLAYA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-5.19015</t>
+          <t>916</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-80.59011</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>-5.18341</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-80.61688</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>820527</t>
+          <t>722471</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>PASITOS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.19608</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-80.59545</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>-5.22012</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-80.62325</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>412765</t>
+          <t>660294</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PROYECTO PESTALOZZI</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-5.19089</t>
+          <t>323</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-80.60785</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>-5.189801</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-80.580096</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,37 +1431,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>796693</t>
+          <t>609366</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>DIVINO NIÑO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.190141</t>
+          <t>319</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-80.58282</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>-5.20865</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-80.62557</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>412402</t>
+          <t>536493</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14114</t>
+          <t>EL TRIUNFO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-5.22446</t>
+          <t>510</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-80.62824</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>-5.197957</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-80.623028</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>412416</t>
+          <t>509102</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>14116 SAN MARTIN DE PORRAS</t>
+          <t>LOS ANGELITOS DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-5.21725</t>
+          <t>759</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-80.62649</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>-5.19121</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-80.60354</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>412567</t>
+          <t>430081</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>15186</t>
+          <t>15419</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-5.04579</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-80.608701</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>-5.14307</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-80.36602</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>412708</t>
+          <t>413072</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MILITAR PEDRO RUIZ GALLO</t>
+          <t>ESTRELLA DE GUADALUPE</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-5.18897</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-80.6009</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>-5.20019</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-80.61901</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1741,37 +1741,37 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>412812</t>
+          <t>413067</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RICARDO PALMA</t>
+          <t>VIRGEN DE LA PUERTA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-5.19846</t>
+          <t>139</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-80.6202</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>-5.205272</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-80.621655</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>766912</t>
+          <t>412930</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>TRILCE DE PIURA</t>
+          <t>SALESIANO DON BOSCO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-5.18708</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-80.62016</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>-5.19533</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-80.62204</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>536493</t>
+          <t>412906</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>EL TRIUNFO</t>
+          <t>FE Y ALEGRIA 15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.197957</t>
+          <t>901</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-80.623028</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>-5.227286</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-80.61153</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>766865</t>
+          <t>412893</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R.M. RAFAELA DE LA PASION VEINTEMILLA</t>
+          <t>ALFONSO UGARTE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-5.18643</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-80.61171</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>-5.19416</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-80.62027</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>412534</t>
+          <t>412888</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>15181</t>
+          <t>JAVIER PEREZ DE CUELLAR</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-5.07948</t>
+          <t>519</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-80.59348</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>-5.18783</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-80.6082</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>412586</t>
+          <t>412845</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>15350 SAN FRANCISCO DE ASIS</t>
+          <t>SAN JUDAS TADEO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-5.18941</t>
+          <t>357</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-80.60686</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>-5.18614</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-80.59293</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>412888</t>
+          <t>412831</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>JAVIER PEREZ DE CUELLAR</t>
+          <t>SAN IGNACIO DE LOYOLA DE PIURA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-5.18783</t>
+          <t>887</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-80.6082</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>-5.187135</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-80.619294</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>412435</t>
+          <t>412826</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>14118 MARINA PURIZACA BENITES</t>
+          <t>SAN GABRIEL</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-5.22685</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-80.61917</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>-5.18503</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-80.62067</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>412609</t>
+          <t>412812</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MARIA GORETTI</t>
+          <t>RICARDO PALMA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-5.190515</t>
+          <t>417</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-80.610261</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>-5.19846</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-80.6202</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>412845</t>
+          <t>412765</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SAN JUDAS TADEO</t>
+          <t>PROYECTO PESTALOZZI</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-5.18614</t>
+          <t>229</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-80.59293</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>-5.19089</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-80.60785</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>412893</t>
+          <t>412708</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ALFONSO UGARTE</t>
+          <t>MILITAR PEDRO RUIZ GALLO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-5.19416</t>
+          <t>244</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-80.62027</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>-5.18897</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-80.6009</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>412628</t>
+          <t>412685</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>20133</t>
+          <t>MANUEL SCORZA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-5.18444</t>
+          <t>638</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-80.5913</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>-5.18625</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-80.60891</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>412633</t>
+          <t>412666</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>SAN JOSE DE TARBES</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-5.19182</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-80.60115</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>-5.19509</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-80.61894</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>412685</t>
+          <t>412652</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MANUEL SCORZA</t>
+          <t>TENIENTE MIGUEL CORTES DEL CASTILLO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-5.18625</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-80.60891</t>
+          <t>89</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>-5.21591</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-80.62369</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>509102</t>
+          <t>412647</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>LOS ANGELITOS DE SAN ANTONIO</t>
+          <t>JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-5.19121</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-80.60354</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>-5.185655</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-80.597749</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>609366</t>
+          <t>412633</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>DIVINO NIÑO</t>
+          <t>20134</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-5.20865</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-80.62557</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>-5.19182</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-80.60115</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>412379</t>
+          <t>412628</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>JOSEMARIA ESCRIVA DE BALAGUER</t>
+          <t>20133</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-5.21052</t>
+          <t>830</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-80.62473</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>-5.18444</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-80.5913</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>858327</t>
+          <t>412614</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>EL TRIUNFO</t>
+          <t>CAP. FAP JOSE ABELARDO QUIÑONES</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-5.20792</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-80.62555</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>-5.18932</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-80.59485</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>852090</t>
+          <t>412609</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>MARIA GORETTI</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-5.18581</t>
+          <t>778</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-80.623</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>-5.190515</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-80.610261</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2929,22 +2929,22 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>1133</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
           <t>-5.18744</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>-80.59259</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1133</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>412906</t>
+          <t>412586</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 15</t>
+          <t>15350 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-5.227286</t>
+          <t>653</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-80.61153</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>-5.18941</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-80.60686</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>412548</t>
+          <t>412567</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SANTISIMA VIRGEN DE GUADALUPE</t>
+          <t>15186</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-4.985086</t>
+          <t>386</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-80.574778</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>-5.04579</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-80.608701</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>412614</t>
+          <t>412548</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CAP. FAP JOSE ABELARDO QUIÑONES</t>
+          <t>SANTISIMA VIRGEN DE GUADALUPE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-5.18932</t>
+          <t>813</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-80.59485</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>-4.985086</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-80.574778</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>864781</t>
+          <t>412534</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>EXITUS</t>
+          <t>15181</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-5.16866</t>
+          <t>531</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-80.61411</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>-5.07948</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-80.59348</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>766064</t>
+          <t>412497</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CARLOTA RAMOS DE SANTOLAYA</t>
+          <t>15015 HEROES DEL CENEPA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-5.18341</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-80.61688</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>-5.19918</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-80.62124</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3301,22 +3301,22 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
+          <t>1056</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
           <t>-5.20703</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>-80.62148</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1056</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>55</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>412826</t>
+          <t>412435</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SAN GABRIEL</t>
+          <t>14118 MARINA PURIZACA BENITES</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-5.18503</t>
+          <t>682</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-80.62067</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>-5.22685</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>-80.61917</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>412355</t>
+          <t>412416</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ALFEREZ FAP SAMUEL ORDOÑEZ VELASQUEZ</t>
+          <t>14116 SAN MARTIN DE PORRAS</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-5.195546</t>
+          <t>444</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-80.618193</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>-5.21725</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-80.62649</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>412341</t>
+          <t>412402</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MARISCAL RAMON CASTILLA</t>
+          <t>14114</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-5.19948</t>
+          <t>438</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-80.62168</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>-5.22446</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-80.62824</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>412831</t>
+          <t>412384</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE LOYOLA DE PIURA</t>
+          <t>14112 AUGUSTO TIMANA SOSA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-5.187135</t>
+          <t>270</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-80.619294</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>-5.21547</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-80.62791</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>412666</t>
+          <t>412379</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SAN JOSE DE TARBES</t>
+          <t>JOSEMARIA ESCRIVA DE BALAGUER</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-5.19509</t>
+          <t>784</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-80.61894</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>-5.21052</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-80.62473</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>722471</t>
+          <t>412355</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>PASITOS</t>
+          <t>ALFEREZ FAP SAMUEL ORDOÑEZ VELASQUEZ</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-5.22012</t>
+          <t>512</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-80.62325</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>-5.195546</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-80.618193</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>412930</t>
+          <t>412341</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SALESIANO DON BOSCO</t>
+          <t>MARISCAL RAMON CASTILLA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-5.19533</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-80.62204</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>-5.19948</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-80.62168</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,37 +3787,37 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>841978</t>
+          <t>412299</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>INTELLECTUS</t>
+          <t>490</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-5.19316</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-80.62066</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>-5.19358</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-80.60787</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>412647</t>
+          <t>412204</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>JOSE CARLOS MARIATEGUI</t>
+          <t>029 SAN BERNARDO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-5.185655</t>
+          <t>208</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-80.597749</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>-5.22292</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>-80.62525</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>412652</t>
+          <t>412195</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TENIENTE MIGUEL CORTES DEL CASTILLO</t>
+          <t>DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-5.21591</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-80.62369</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>-5.2261</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>-80.61923</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3983,22 +3983,22 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
           <t>-5.19463</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>-80.61998</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>412204</t>
+          <t>032082</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>029 SAN BERNARDO</t>
+          <t>PITAGORAS</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-5.22292</t>
+          <t>291</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-80.62525</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>-5.19107</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-80.60361</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">

--- a/ZonasEscolares/excels/PIURA-PIURA-CASTILLA.xlsx
+++ b/ZonasEscolares/excels/PIURA-PIURA-CASTILLA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
